--- a/artfynd/A 37896-2022 artfynd.xlsx
+++ b/artfynd/A 37896-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 37896-2022 artfynd.xlsx
+++ b/artfynd/A 37896-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY191"/>
+  <dimension ref="A1:AY195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22736,6 +22736,423 @@
       </c>
       <c r="AY191" t="inlineStr"/>
     </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>114899127</v>
+      </c>
+      <c r="B192" t="n">
+        <v>57385</v>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E192" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr"/>
+      <c r="K192" t="inlineStr"/>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>Rosendal, Sm</t>
+        </is>
+      </c>
+      <c r="Q192" t="n">
+        <v>571035</v>
+      </c>
+      <c r="R192" t="n">
+        <v>6376943</v>
+      </c>
+      <c r="S192" t="n">
+        <v>25</v>
+      </c>
+      <c r="T192" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U192" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V192" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W192" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y192" t="inlineStr">
+        <is>
+          <t>2024-02-27</t>
+        </is>
+      </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>2024-02-27</t>
+        </is>
+      </c>
+      <c r="AD192" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE192" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG192" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT192" t="inlineStr"/>
+      <c r="AW192" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX192" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>114898619</v>
+      </c>
+      <c r="B193" t="n">
+        <v>90241</v>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E193" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr"/>
+      <c r="K193" t="inlineStr"/>
+      <c r="P193" t="inlineStr">
+        <is>
+          <t>Rosendal, Sm</t>
+        </is>
+      </c>
+      <c r="Q193" t="n">
+        <v>570886</v>
+      </c>
+      <c r="R193" t="n">
+        <v>6377039</v>
+      </c>
+      <c r="S193" t="n">
+        <v>25</v>
+      </c>
+      <c r="T193" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U193" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V193" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W193" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y193" t="inlineStr">
+        <is>
+          <t>2024-02-27</t>
+        </is>
+      </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>2024-02-27</t>
+        </is>
+      </c>
+      <c r="AD193" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE193" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG193" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT193" t="inlineStr"/>
+      <c r="AW193" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX193" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>114899311</v>
+      </c>
+      <c r="B194" t="n">
+        <v>74589</v>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E194" t="n">
+        <v>308</v>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr"/>
+      <c r="K194" t="inlineStr"/>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>Rosendal, Sm</t>
+        </is>
+      </c>
+      <c r="Q194" t="n">
+        <v>571139</v>
+      </c>
+      <c r="R194" t="n">
+        <v>6376876</v>
+      </c>
+      <c r="S194" t="n">
+        <v>25</v>
+      </c>
+      <c r="T194" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U194" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V194" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W194" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y194" t="inlineStr">
+        <is>
+          <t>2024-02-27</t>
+        </is>
+      </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>2024-02-27</t>
+        </is>
+      </c>
+      <c r="AD194" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE194" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG194" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT194" t="inlineStr"/>
+      <c r="AW194" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX194" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>114900051</v>
+      </c>
+      <c r="B195" t="n">
+        <v>90261</v>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E195" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr"/>
+      <c r="K195" t="inlineStr"/>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>Rosendal, Sm</t>
+        </is>
+      </c>
+      <c r="Q195" t="n">
+        <v>570880</v>
+      </c>
+      <c r="R195" t="n">
+        <v>6377026</v>
+      </c>
+      <c r="S195" t="n">
+        <v>25</v>
+      </c>
+      <c r="T195" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V195" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W195" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y195" t="inlineStr">
+        <is>
+          <t>2024-02-27</t>
+        </is>
+      </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>2024-02-27</t>
+        </is>
+      </c>
+      <c r="AD195" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE195" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG195" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT195" t="inlineStr"/>
+      <c r="AW195" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX195" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY195" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37896-2022 artfynd.xlsx
+++ b/artfynd/A 37896-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY195"/>
+  <dimension ref="A1:AY199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23153,6 +23153,463 @@
       </c>
       <c r="AY195" t="inlineStr"/>
     </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>114932845</v>
+      </c>
+      <c r="B196" t="n">
+        <v>5345</v>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E196" t="n">
+        <v>101728</v>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Grön aspvedbock</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>Saperda perforata</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>(Pallas, 1773)</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr"/>
+      <c r="K196" t="inlineStr"/>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>Rosendal, Sm</t>
+        </is>
+      </c>
+      <c r="Q196" t="n">
+        <v>570518</v>
+      </c>
+      <c r="R196" t="n">
+        <v>6377417</v>
+      </c>
+      <c r="S196" t="n">
+        <v>25</v>
+      </c>
+      <c r="T196" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U196" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V196" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W196" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y196" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="Z196" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AB196" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AC196" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
+        </is>
+      </c>
+      <c r="AD196" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE196" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG196" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT196" t="inlineStr"/>
+      <c r="AW196" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX196" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>114932339</v>
+      </c>
+      <c r="B197" t="n">
+        <v>94037</v>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E197" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr"/>
+      <c r="K197" t="inlineStr"/>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t>Rosendal, Sm</t>
+        </is>
+      </c>
+      <c r="Q197" t="n">
+        <v>570604</v>
+      </c>
+      <c r="R197" t="n">
+        <v>6377344</v>
+      </c>
+      <c r="S197" t="n">
+        <v>25</v>
+      </c>
+      <c r="T197" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U197" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V197" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W197" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y197" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="Z197" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AB197" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AD197" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE197" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG197" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT197" t="inlineStr"/>
+      <c r="AW197" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX197" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>114932412</v>
+      </c>
+      <c r="B198" t="n">
+        <v>90202</v>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E198" t="n">
+        <v>5445</v>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Ekticka</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Fomitiporia robusta</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr"/>
+      <c r="K198" t="inlineStr"/>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>Rosendal, Sm</t>
+        </is>
+      </c>
+      <c r="Q198" t="n">
+        <v>570564</v>
+      </c>
+      <c r="R198" t="n">
+        <v>6377380</v>
+      </c>
+      <c r="S198" t="n">
+        <v>25</v>
+      </c>
+      <c r="T198" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V198" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W198" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y198" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="Z198" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AB198" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AD198" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE198" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG198" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT198" t="inlineStr"/>
+      <c r="AW198" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX198" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>114932365</v>
+      </c>
+      <c r="B199" t="n">
+        <v>89666</v>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E199" t="n">
+        <v>5685</v>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Gullgröppa</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>Pseudomerulius aureus</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr"/>
+      <c r="K199" t="inlineStr"/>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>Rosendal, Sm</t>
+        </is>
+      </c>
+      <c r="Q199" t="n">
+        <v>570587</v>
+      </c>
+      <c r="R199" t="n">
+        <v>6377349</v>
+      </c>
+      <c r="S199" t="n">
+        <v>25</v>
+      </c>
+      <c r="T199" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V199" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W199" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y199" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="Z199" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AB199" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AD199" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE199" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG199" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT199" t="inlineStr"/>
+      <c r="AW199" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX199" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY199" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37896-2022 artfynd.xlsx
+++ b/artfynd/A 37896-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY199"/>
+  <dimension ref="A1:AY201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23610,6 +23610,239 @@
       </c>
       <c r="AY199" t="inlineStr"/>
     </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>114943740</v>
+      </c>
+      <c r="B200" t="n">
+        <v>94044</v>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E200" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr"/>
+      <c r="J200" t="inlineStr"/>
+      <c r="K200" t="inlineStr"/>
+      <c r="L200" t="inlineStr"/>
+      <c r="N200" t="inlineStr"/>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>Väderum, smedserum, Sm</t>
+        </is>
+      </c>
+      <c r="Q200" t="n">
+        <v>570599</v>
+      </c>
+      <c r="R200" t="n">
+        <v>6377338</v>
+      </c>
+      <c r="S200" t="n">
+        <v>25</v>
+      </c>
+      <c r="T200" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U200" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V200" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W200" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y200" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="Z200" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AB200" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD200" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE200" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF200" t="inlineStr"/>
+      <c r="AG200" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT200" t="inlineStr"/>
+      <c r="AW200" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX200" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>114943894</v>
+      </c>
+      <c r="B201" t="n">
+        <v>90209</v>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E201" t="n">
+        <v>5445</v>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Ekticka</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Fomitiporia robusta</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr"/>
+      <c r="J201" t="inlineStr"/>
+      <c r="K201" t="inlineStr"/>
+      <c r="N201" t="inlineStr"/>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>Väderum, smedserum, Sm</t>
+        </is>
+      </c>
+      <c r="Q201" t="n">
+        <v>570570</v>
+      </c>
+      <c r="R201" t="n">
+        <v>6377386</v>
+      </c>
+      <c r="S201" t="n">
+        <v>25</v>
+      </c>
+      <c r="T201" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U201" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V201" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W201" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y201" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="Z201" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AB201" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD201" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE201" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF201" t="inlineStr"/>
+      <c r="AG201" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT201" t="inlineStr"/>
+      <c r="AW201" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX201" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY201" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37896-2022 artfynd.xlsx
+++ b/artfynd/A 37896-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY201"/>
+  <dimension ref="A1:AY202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23155,10 +23155,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>114932845</v>
+        <v>114899152</v>
       </c>
       <c r="B196" t="n">
-        <v>5345</v>
+        <v>57597</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -23167,25 +23167,25 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>101728</v>
+        <v>103015</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -23196,10 +23196,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>570518</v>
+        <v>571062</v>
       </c>
       <c r="R196" t="n">
-        <v>6377417</v>
+        <v>6376956</v>
       </c>
       <c r="S196" t="n">
         <v>25</v>
@@ -23226,27 +23226,12 @@
       </c>
       <c r="Y196" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
-        </is>
-      </c>
-      <c r="Z196" t="inlineStr">
-        <is>
-          <t>14:52</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
-        </is>
-      </c>
-      <c r="AB196" t="inlineStr">
-        <is>
-          <t>14:52</t>
-        </is>
-      </c>
-      <c r="AC196" t="inlineStr">
-        <is>
-          <t>Kläckhål</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -23273,10 +23258,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>114932339</v>
+        <v>114932845</v>
       </c>
       <c r="B197" t="n">
-        <v>94037</v>
+        <v>5345</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -23285,25 +23270,25 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>2671</v>
+        <v>101728</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -23314,10 +23299,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>570604</v>
+        <v>570518</v>
       </c>
       <c r="R197" t="n">
-        <v>6377344</v>
+        <v>6377417</v>
       </c>
       <c r="S197" t="n">
         <v>25</v>
@@ -23349,7 +23334,7 @@
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
@@ -23359,7 +23344,12 @@
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AC197" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -23386,10 +23376,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>114932412</v>
+        <v>114932339</v>
       </c>
       <c r="B198" t="n">
-        <v>90202</v>
+        <v>94037</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -23398,25 +23388,25 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>5445</v>
+        <v>2671</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -23427,10 +23417,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>570564</v>
+        <v>570604</v>
       </c>
       <c r="R198" t="n">
-        <v>6377380</v>
+        <v>6377344</v>
       </c>
       <c r="S198" t="n">
         <v>25</v>
@@ -23499,10 +23489,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>114932365</v>
+        <v>114932412</v>
       </c>
       <c r="B199" t="n">
-        <v>89666</v>
+        <v>90202</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -23511,25 +23501,25 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>5685</v>
+        <v>5445</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -23540,10 +23530,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>570587</v>
+        <v>570564</v>
       </c>
       <c r="R199" t="n">
-        <v>6377349</v>
+        <v>6377380</v>
       </c>
       <c r="S199" t="n">
         <v>25</v>
@@ -23612,10 +23602,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>114943740</v>
+        <v>114932365</v>
       </c>
       <c r="B200" t="n">
-        <v>94044</v>
+        <v>89666</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -23628,38 +23618,35 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>2671</v>
+        <v>5685</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
-      <c r="J200" t="inlineStr"/>
       <c r="K200" t="inlineStr"/>
-      <c r="L200" t="inlineStr"/>
-      <c r="N200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
-          <t>Väderum, smedserum, Sm</t>
+          <t>Rosendal, Sm</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>570599</v>
+        <v>570587</v>
       </c>
       <c r="R200" t="n">
-        <v>6377338</v>
+        <v>6377349</v>
       </c>
       <c r="S200" t="n">
         <v>25</v>
@@ -23691,7 +23678,7 @@
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
@@ -23701,7 +23688,7 @@
       </c>
       <c r="AB200" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -23710,29 +23697,28 @@
       <c r="AE200" t="b">
         <v>0</v>
       </c>
-      <c r="AF200" t="inlineStr"/>
       <c r="AG200" t="b">
         <v>0</v>
       </c>
       <c r="AT200" t="inlineStr"/>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>114943894</v>
+        <v>114943740</v>
       </c>
       <c r="B201" t="n">
-        <v>90209</v>
+        <v>94044</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -23741,30 +23727,31 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>5445</v>
+        <v>2671</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
       <c r="J201" t="inlineStr"/>
       <c r="K201" t="inlineStr"/>
+      <c r="L201" t="inlineStr"/>
       <c r="N201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
@@ -23772,10 +23759,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>570570</v>
+        <v>570599</v>
       </c>
       <c r="R201" t="n">
-        <v>6377386</v>
+        <v>6377338</v>
       </c>
       <c r="S201" t="n">
         <v>25</v>
@@ -23842,6 +23829,122 @@
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>114943894</v>
+      </c>
+      <c r="B202" t="n">
+        <v>90209</v>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E202" t="n">
+        <v>5445</v>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Ekticka</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Fomitiporia robusta</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr"/>
+      <c r="J202" t="inlineStr"/>
+      <c r="K202" t="inlineStr"/>
+      <c r="N202" t="inlineStr"/>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>Väderum, smedserum, Sm</t>
+        </is>
+      </c>
+      <c r="Q202" t="n">
+        <v>570570</v>
+      </c>
+      <c r="R202" t="n">
+        <v>6377386</v>
+      </c>
+      <c r="S202" t="n">
+        <v>25</v>
+      </c>
+      <c r="T202" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U202" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V202" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W202" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y202" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="Z202" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AB202" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD202" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE202" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF202" t="inlineStr"/>
+      <c r="AG202" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT202" t="inlineStr"/>
+      <c r="AW202" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX202" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY202" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 37896-2022 artfynd.xlsx
+++ b/artfynd/A 37896-2022 artfynd.xlsx
@@ -22741,7 +22741,7 @@
         <v>114899127</v>
       </c>
       <c r="B192" t="n">
-        <v>57527</v>
+        <v>57532</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>

--- a/artfynd/A 37896-2022 artfynd.xlsx
+++ b/artfynd/A 37896-2022 artfynd.xlsx
@@ -22756,11 +22756,6 @@
       <c r="E192" t="n">
         <v>103021</v>
       </c>
-      <c r="F192" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
       <c r="G192" t="inlineStr">
         <is>
           <t>Poecile montanus</t>

--- a/artfynd/A 37896-2022 artfynd.xlsx
+++ b/artfynd/A 37896-2022 artfynd.xlsx
@@ -22741,7 +22741,7 @@
         <v>114899127</v>
       </c>
       <c r="B192" t="n">
-        <v>57532</v>
+        <v>57536</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -22755,6 +22755,11 @@
       </c>
       <c r="E192" t="n">
         <v>103021</v>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>

--- a/artfynd/A 37896-2022 artfynd.xlsx
+++ b/artfynd/A 37896-2022 artfynd.xlsx
@@ -22741,7 +22741,7 @@
         <v>114899127</v>
       </c>
       <c r="B192" t="n">
-        <v>57536</v>
+        <v>57537</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>

--- a/artfynd/A 37896-2022 artfynd.xlsx
+++ b/artfynd/A 37896-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY207"/>
+  <dimension ref="A1:AY206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2560,10 +2560,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>106853580</v>
+        <v>116075979</v>
       </c>
       <c r="B18" t="n">
-        <v>89832</v>
+        <v>90783</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2594,20 +2594,26 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Väderum, Sm</t>
+          <t>Gallsjöskogen, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>570251.4842030325</v>
+        <v>570251</v>
       </c>
       <c r="R18" t="n">
-        <v>6377394.823069351</v>
+        <v>6377395</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2631,22 +2637,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-02-18</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-02-18</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2655,18 +2651,34 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -24301,10 +24313,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>116075979</v>
+        <v>116143788</v>
       </c>
       <c r="B206" t="n">
-        <v>90783</v>
+        <v>90795</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -24317,21 +24329,21 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>1209</v>
+        <v>1506</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -24348,13 +24360,13 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>570251</v>
+        <v>570365</v>
       </c>
       <c r="R206" t="n">
-        <v>6377395</v>
+        <v>6377400</v>
       </c>
       <c r="S206" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T206" t="inlineStr">
         <is>
@@ -24384,6 +24396,11 @@
       <c r="AA206" t="inlineStr">
         <is>
           <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="AC206" t="inlineStr">
+        <is>
+          <t>asplåga</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -24396,21 +24413,6 @@
       <c r="AG206" t="b">
         <v>0</v>
       </c>
-      <c r="AJ206" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK206" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO206" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT206" t="inlineStr"/>
       <c r="AW206" t="inlineStr">
         <is>
@@ -24423,121 +24425,6 @@
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
-    </row>
-    <row r="207">
-      <c r="A207" t="n">
-        <v>116143788</v>
-      </c>
-      <c r="B207" t="n">
-        <v>90795</v>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E207" t="n">
-        <v>1506</v>
-      </c>
-      <c r="F207" t="inlineStr">
-        <is>
-          <t>Ostticka</t>
-        </is>
-      </c>
-      <c r="G207" t="inlineStr">
-        <is>
-          <t>Skeletocutis odora</t>
-        </is>
-      </c>
-      <c r="H207" t="inlineStr">
-        <is>
-          <t>(Sacc.) Ginns</t>
-        </is>
-      </c>
-      <c r="I207" t="inlineStr"/>
-      <c r="J207" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K207" t="inlineStr"/>
-      <c r="N207" t="inlineStr"/>
-      <c r="P207" t="inlineStr">
-        <is>
-          <t>Gallsjöskogen, Sm</t>
-        </is>
-      </c>
-      <c r="Q207" t="n">
-        <v>570365</v>
-      </c>
-      <c r="R207" t="n">
-        <v>6377400</v>
-      </c>
-      <c r="S207" t="n">
-        <v>25</v>
-      </c>
-      <c r="T207" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U207" t="inlineStr">
-        <is>
-          <t>Vimmerby</t>
-        </is>
-      </c>
-      <c r="V207" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W207" t="inlineStr">
-        <is>
-          <t>Tuna</t>
-        </is>
-      </c>
-      <c r="Y207" t="inlineStr">
-        <is>
-          <t>2024-04-17</t>
-        </is>
-      </c>
-      <c r="AA207" t="inlineStr">
-        <is>
-          <t>2024-04-17</t>
-        </is>
-      </c>
-      <c r="AC207" t="inlineStr">
-        <is>
-          <t>asplåga</t>
-        </is>
-      </c>
-      <c r="AD207" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE207" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF207" t="inlineStr"/>
-      <c r="AG207" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT207" t="inlineStr"/>
-      <c r="AW207" t="inlineStr">
-        <is>
-          <t>Stefan Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AX207" t="inlineStr">
-        <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AY207" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 37896-2022 artfynd.xlsx
+++ b/artfynd/A 37896-2022 artfynd.xlsx
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="AE25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG25" t="b">
         <v>0</v>
@@ -6035,7 +6035,7 @@
         <v>0</v>
       </c>
       <c r="AE47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG47" t="b">
         <v>0</v>
@@ -7069,7 +7069,7 @@
         <v>0</v>
       </c>
       <c r="AE56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG56" t="b">
         <v>0</v>

--- a/artfynd/A 37896-2022 artfynd.xlsx
+++ b/artfynd/A 37896-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY233"/>
+  <dimension ref="A1:AZ233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106853820</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -868,6 +878,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106854488</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -970,6 +985,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610093</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1072,6 +1092,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610094</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1174,6 +1199,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610096</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1276,6 +1306,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610193</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1378,6 +1413,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610194</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610158</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1582,6 +1627,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106850618</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1680,6 +1730,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106853524</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1778,6 +1833,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106853664</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1889,6 +1949,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106866010</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1991,6 +2056,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610021</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2093,6 +2163,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610022</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2195,6 +2270,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610024</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2297,6 +2377,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610025</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2417,6 +2502,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116076055</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2515,6 +2605,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106853580</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2617,6 +2712,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610051</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2719,6 +2819,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610062</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2821,6 +2926,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610063</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2923,6 +3033,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610064</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3025,6 +3140,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610065</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3127,6 +3247,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610066</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3237,6 +3362,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116143788</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3339,6 +3469,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610210</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3441,6 +3576,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610052</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3553,6 +3693,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106850109</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3651,6 +3796,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106854870</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3748,6 +3898,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610222</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3845,6 +4000,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610167</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3954,6 +4114,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116073260</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4057,6 +4222,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610227</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4155,6 +4325,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106854304</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4252,6 +4427,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106850620</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4350,6 +4530,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106853269</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4448,6 +4633,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106853724</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4546,6 +4736,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106853798</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4644,6 +4839,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106853825</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4746,6 +4946,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106854897</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4848,6 +5053,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106854965</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4963,6 +5173,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106865985</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5078,6 +5293,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106866002</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5193,6 +5413,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106866026</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5308,6 +5533,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106866100</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5423,6 +5653,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106866107</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5520,6 +5755,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610031</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5640,6 +5880,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106866051</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5737,6 +5982,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610173</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5834,6 +6084,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610174</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5931,6 +6186,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610178</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6028,6 +6288,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610179</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6130,6 +6395,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610056</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6232,6 +6502,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610121</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6334,6 +6609,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610122</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6436,6 +6716,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610124</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6538,6 +6823,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610127</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6640,6 +6930,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610041</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6742,6 +7037,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610009</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6861,6 +7161,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106850075</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6964,6 +7269,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106853451</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7066,6 +7376,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106862274</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7169,6 +7484,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106853706</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7272,6 +7592,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106847453</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7369,6 +7694,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610207</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7466,6 +7796,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106850621</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7564,6 +7899,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106854306</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7667,6 +8007,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106855292</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7770,6 +8115,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106847464</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7867,6 +8217,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610014</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7970,6 +8325,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106847279</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8068,6 +8428,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106847682</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8184,6 +8549,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106850122</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8300,6 +8670,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106850180</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8416,6 +8791,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106850186</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8518,6 +8898,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106850622</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8620,6 +9005,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106850623</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8722,6 +9112,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106850624</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8824,6 +9219,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106850625</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8926,6 +9326,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106850626</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9024,6 +9429,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106852503</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9127,6 +9537,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106853695</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9225,6 +9640,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106854174</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9327,6 +9747,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106854200</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9430,6 +9855,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106854284</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9532,6 +9962,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106854299</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9630,6 +10065,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106854311</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9732,6 +10172,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106854332</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9834,6 +10279,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106854385</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9944,6 +10394,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106861736</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10054,6 +10509,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106861801</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10156,6 +10616,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106862302</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10264,6 +10729,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107289239</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10362,6 +10832,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107300003</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10474,6 +10949,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107383910</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10576,6 +11056,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610104</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10678,6 +11163,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610105</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10775,6 +11265,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610106</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10872,6 +11367,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610138</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10970,6 +11470,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106853694</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11087,6 +11592,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106865955</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11204,6 +11714,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106866116</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11306,6 +11821,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610005</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11408,6 +11928,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610006</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11506,6 +12031,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106857303</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11608,6 +12138,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610145</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11706,6 +12241,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114899311</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11804,6 +12344,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106856173</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11915,6 +12460,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106866135</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12017,6 +12567,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610195</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12119,6 +12674,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610197</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12221,6 +12781,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610198</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12323,6 +12888,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610199</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12440,6 +13010,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106856171</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12542,6 +13117,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610023</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12644,6 +13224,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610026</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12742,6 +13327,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114898619</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12844,6 +13434,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610075</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12942,6 +13537,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106858652</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13044,6 +13644,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610214</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13142,6 +13747,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106856317</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13254,6 +13864,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106866137</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13352,6 +13967,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106855693</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13450,6 +14070,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106855711</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13562,6 +14187,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106866172</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13659,6 +14289,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610169</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13767,6 +14402,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114932339</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13879,6 +14519,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114943740</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -13987,6 +14632,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106857826</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -14089,6 +14739,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610037</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14191,6 +14846,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106856685</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14294,6 +14954,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610228</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14392,6 +15057,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106853239</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -14509,6 +15179,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106855023</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -14611,6 +15286,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106856200</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14709,6 +15389,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106856376</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14807,6 +15492,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106856505</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -14905,6 +15595,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106857816</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -15002,6 +15697,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106862265</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -15113,6 +15813,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106865958</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -15210,6 +15915,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610029</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -15307,6 +16017,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610030</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -15405,6 +16120,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114900051</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -15512,6 +16232,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115739760</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -15627,6 +16352,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106866082</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -15724,6 +16454,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610180</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -15832,6 +16567,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114932412</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -15943,6 +16683,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114943894</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -16045,6 +16790,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610128</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -16153,6 +16903,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114932365</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -16268,6 +17023,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106866257</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -16370,6 +17130,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610057</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -16481,6 +17246,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106865967</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -16583,6 +17353,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610008</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -16685,6 +17460,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610010</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -16787,6 +17567,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610190</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -16889,6 +17674,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610191</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -17002,6 +17792,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106854222</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -17115,6 +17910,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106853583</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -17228,6 +18028,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106853934</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -17331,6 +18136,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106855529</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -17433,6 +18243,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106862270</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -17535,6 +18350,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106862271</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -17637,6 +18457,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106862272</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -17739,6 +18564,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106862273</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -17842,6 +18672,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106857259</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -17939,6 +18774,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610206</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -18036,6 +18876,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106862289</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -18133,6 +18978,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106862290</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -18230,6 +19080,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106862292</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -18328,6 +19183,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114899152</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -18445,6 +19305,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106854082</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -18552,6 +19417,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106856347</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -18657,6 +19527,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114899127</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -18765,6 +19640,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106854243</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -18878,6 +19758,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114932471</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -18981,6 +19866,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106852922</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -19083,6 +19973,11 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610045</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -19180,6 +20075,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610042</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -19283,6 +20183,11 @@
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106853018</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -19385,6 +20290,11 @@
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106853042</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -19483,6 +20393,11 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106855792</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -19581,6 +20496,11 @@
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106855880</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -19683,6 +20603,11 @@
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106855992</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -19786,6 +20711,11 @@
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106855995</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -19888,6 +20818,11 @@
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106856119</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -19991,6 +20926,11 @@
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106856125</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -20093,6 +21033,11 @@
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106856160</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -20196,6 +21141,11 @@
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106856263</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -20298,6 +21248,11 @@
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106856290</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -20401,6 +21356,11 @@
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106856359</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -20499,6 +21459,11 @@
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106856561</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -20601,6 +21566,11 @@
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106856643</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -20718,6 +21688,11 @@
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106856644</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -20820,6 +21795,11 @@
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106856705</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -20918,6 +21898,11 @@
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106856743</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -21035,6 +22020,11 @@
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106856774</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -21137,6 +22127,11 @@
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106857555</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -21239,6 +22234,11 @@
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106857984</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -21341,6 +22341,11 @@
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106858882</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -21443,6 +22448,11 @@
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106862300</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -21545,6 +22555,11 @@
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106862301</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -21647,6 +22662,11 @@
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106862303</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -21749,6 +22769,11 @@
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106862304</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -21846,6 +22871,11 @@
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610097</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -21943,6 +22973,11 @@
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610098</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -22040,6 +23075,11 @@
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610099</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -22137,6 +23177,11 @@
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610100</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -22234,6 +23279,11 @@
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610101</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -22336,6 +23386,11 @@
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610102</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -22433,6 +23488,11 @@
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610103</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -22531,6 +23591,11 @@
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106857577</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -22633,6 +23698,11 @@
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106857667</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -22750,6 +23820,11 @@
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106857245</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -22847,6 +23922,11 @@
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106862275</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -22944,6 +24024,11 @@
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106862276</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -23041,6 +24126,11 @@
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106862280</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -23138,6 +24228,11 @@
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106862281</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -23235,6 +24330,11 @@
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610110</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -23343,6 +24443,11 @@
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106853952</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -23451,6 +24556,11 @@
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106853984</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -23559,6 +24669,11 @@
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106855677</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -23657,6 +24772,11 @@
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106856753</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -23755,6 +24875,11 @@
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106858362</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -23852,6 +24977,11 @@
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106862307</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -23949,6 +25079,11 @@
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106862308</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -24046,6 +25181,11 @@
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106862309</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -24143,6 +25283,11 @@
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106862310</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -24240,6 +25385,11 @@
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106862311</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -24337,6 +25487,11 @@
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106862312</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -24434,6 +25589,11 @@
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610221</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -24536,8 +25696,247 @@
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610131</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ233" r:id="rId232"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>